--- a/Padrao/Leiautes/Tabela de Preços/Pacotes/PRESTADOR/Leiaute de Pacotes e itens do pacote no prestador.xlsx
+++ b/Padrao/Leiautes/Tabela de Preços/Pacotes/PRESTADOR/Leiaute de Pacotes e itens do pacote no prestador.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="287">
   <si>
     <t>TABELA</t>
   </si>
@@ -96,18 +96,12 @@
     <t>Inteiro</t>
   </si>
   <si>
-    <t>Idade final em anos, para o respectivo preço</t>
-  </si>
-  <si>
     <t>ATEDIAS</t>
   </si>
   <si>
     <t>Dias</t>
   </si>
   <si>
-    <t>Idade final em dias, para o respectivo preço</t>
-  </si>
-  <si>
     <t>CONVENIO</t>
   </si>
   <si>
@@ -144,15 +138,9 @@
     <t>DEANOS</t>
   </si>
   <si>
-    <t>Idade inicial em anos, para o respectivo preço</t>
-  </si>
-  <si>
     <t>DEDIAS</t>
   </si>
   <si>
-    <t>Idade inicial em dias, para o respectivo preço</t>
-  </si>
-  <si>
     <t>ESTRUTURAEVENTO</t>
   </si>
   <si>
@@ -211,18 +199,12 @@
   </si>
   <si>
     <t>APARTAMENTO</t>
-  </si>
-  <si>
-    <t>Acomodação do pacote negociado. Se necessário, codigo da tabela de acomodações</t>
   </si>
   <si>
     <t>Nenhum -1
 Idade do beneficiário atendido - 2</t>
   </si>
   <si>
-    <t>Se 2, exigira o preenchimento de  DEANOS, DEDIAS , ATEANOS, ATEDIAS</t>
-  </si>
-  <si>
     <t>Se TABNEGOCIACAO = 2</t>
   </si>
   <si>
@@ -250,9 +232,6 @@
     <t xml:space="preserve"> Descrição</t>
   </si>
   <si>
-    <t xml:space="preserve"> PACOTE</t>
-  </si>
-  <si>
     <t xml:space="preserve"> PACOTE ODONTOLÓGICO</t>
   </si>
   <si>
@@ -271,9 +250,6 @@
     <t>SAM_PERCENTUALPGTO</t>
   </si>
   <si>
-    <t>Código de Pagamento para o evento no pacote</t>
-  </si>
-  <si>
     <t>CODIGOTABELATISS</t>
   </si>
   <si>
@@ -310,9 +286,6 @@
     <t>Lógico</t>
   </si>
   <si>
-    <t>Indica se Permite cobrança fora do pacote</t>
-  </si>
-  <si>
     <t>QTDUSCUSTOOPERACIONAL</t>
   </si>
   <si>
@@ -322,18 +295,12 @@
     <t>Número</t>
   </si>
   <si>
-    <t>Quantidade de US para custo operacionla no pacote</t>
-  </si>
-  <si>
     <t>QTDUSHONORARIO</t>
   </si>
   <si>
     <t>Qtd Us Honorários</t>
   </si>
   <si>
-    <t>Quantidade de US para honorários no pacote</t>
-  </si>
-  <si>
     <t>QUANTIDADE</t>
   </si>
   <si>
@@ -349,9 +316,6 @@
     <t>Excluir da TGE Complementar</t>
   </si>
   <si>
-    <t>Indica se deve excluir da TGE complementar</t>
-  </si>
-  <si>
     <t>TABELACUSTOOPERAC</t>
   </si>
   <si>
@@ -424,9 +388,6 @@
     <t>CODIGO TABELA TISS</t>
   </si>
   <si>
-    <t>Evento a Gerar no pacote  - mesmo item da linha EVENTOAGERAR</t>
-  </si>
-  <si>
     <t>MASCARATGEITEM</t>
   </si>
   <si>
@@ -890,13 +851,79 @@
   </si>
   <si>
     <t>061</t>
+  </si>
+  <si>
+    <t>Acomodação do pacote negociado. Se necessário, codigo da tabela de acomodações. Para saude petro, enviar vazio na migração</t>
+  </si>
+  <si>
+    <t>Se 2, exigira o preenchimento de  DEANOS, DEDIAS , ATEANOS, ATEDIAS - Fixo 1 - Nenhum</t>
+  </si>
+  <si>
+    <t>Idade final em anos, para o respectivo preço. Enviar Vazio pois TABNEGOCIACAO fixo 1</t>
+  </si>
+  <si>
+    <t>Idade final em dias, para o respectivo preço. Enviar Vazio pois TABNEGOCIACAO fixo 1</t>
+  </si>
+  <si>
+    <t>Idade inicial em anos, para o respectivo preço Enviar Vazio pois TABNEGOCIACAO fixo 1</t>
+  </si>
+  <si>
+    <t>Idade inicial em dias, para o respectivo preço.  Enviar Vazio pois TABNEGOCIACAO fixo 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PACOTE MEDICO</t>
+  </si>
+  <si>
+    <t>Código de Pagamento para o evento no pacote -  Fixo 1</t>
+  </si>
+  <si>
+    <t>Evento a Gerar no pacote</t>
+  </si>
+  <si>
+    <t>Indica se Permite cobrança fora do pacote -  Fixo S</t>
+  </si>
+  <si>
+    <t>Indica se deve excluir da TGE complementar Fixo N</t>
+  </si>
+  <si>
+    <r>
+      <t>Quantidade de US para custo operacionla no pacote -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> VALIDAÇÃO COM NORMAS TECNICAS SE CALCULO DE PF TEM BASE NO VALOR DO ITEM DO PACOTE OU NA SOMATORIA DE ITENS DO PACOTE, POIS SE BASE FOR A SOMATORIA, VALORES SERÃO RATEADOS ENTRE OS ITENS DO PACOTE</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Quantidade de US para honorários no pacote - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>VALIDAÇÃO COM NORMAS TECNICAS SE CALCULO DE PF TEM BASE NO VALOR DO ITEM DO PACOTE OU NA SOMATORIA DE ITENS DO PACOTE, POIS SE BASE FOR A SOMATORIA, VALORES SERÃO RATEADOS ENTRE OS ITENS DO PACOTE</t>
+    </r>
+  </si>
+  <si>
+    <t>Unidade de Medida - Enviar Vazio</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -915,6 +942,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1237,7 +1271,7 @@
     <col min="1" max="1" width="44.33203125" customWidth="1"/>
     <col min="2" max="2" width="24.5546875" customWidth="1"/>
     <col min="3" max="3" width="20.21875" customWidth="1"/>
-    <col min="10" max="10" width="33.5546875" customWidth="1"/>
+    <col min="10" max="10" width="33.5546875" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
@@ -1304,7 +1338,7 @@
         <v>17</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>60</v>
+        <v>273</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
@@ -1324,13 +1358,13 @@
         <v>20</v>
       </c>
       <c r="F3" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="G3" t="s">
         <v>16</v>
       </c>
       <c r="L3" t="s">
-        <v>21</v>
+        <v>275</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
@@ -1338,10 +1372,10 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
         <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1350,13 +1384,13 @@
         <v>20</v>
       </c>
       <c r="F4" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="G4" t="s">
         <v>16</v>
       </c>
       <c r="L4" t="s">
-        <v>24</v>
+        <v>276</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
@@ -1364,10 +1398,10 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D5">
         <v>6</v>
@@ -1376,16 +1410,16 @@
         <v>15</v>
       </c>
       <c r="F5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G5" t="s">
         <v>16</v>
       </c>
       <c r="I5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L5" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
@@ -1393,16 +1427,16 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D6">
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F6" t="s">
         <v>16</v>
@@ -1411,7 +1445,7 @@
         <v>16</v>
       </c>
       <c r="L6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
@@ -1419,25 +1453,25 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D7">
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G7" t="s">
         <v>16</v>
       </c>
       <c r="L7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
@@ -1445,7 +1479,7 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
         <v>19</v>
@@ -1457,13 +1491,13 @@
         <v>20</v>
       </c>
       <c r="F8" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="G8" t="s">
         <v>16</v>
       </c>
       <c r="L8" t="s">
-        <v>37</v>
+        <v>277</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
@@ -1471,10 +1505,10 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1483,13 +1517,13 @@
         <v>20</v>
       </c>
       <c r="F9" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="G9" t="s">
         <v>16</v>
       </c>
       <c r="L9" t="s">
-        <v>39</v>
+        <v>278</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
@@ -1497,10 +1531,10 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D10">
         <v>6</v>
@@ -1509,16 +1543,16 @@
         <v>15</v>
       </c>
       <c r="F10" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G10" t="s">
         <v>16</v>
       </c>
       <c r="I10" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="L10" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
@@ -1526,10 +1560,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C11" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D11">
         <v>6</v>
@@ -1538,16 +1572,16 @@
         <v>15</v>
       </c>
       <c r="F11" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G11" t="s">
         <v>16</v>
       </c>
       <c r="I11" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="L11" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
@@ -1555,10 +1589,10 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C12" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D12">
         <v>6</v>
@@ -1567,16 +1601,16 @@
         <v>15</v>
       </c>
       <c r="F12" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G12" t="s">
         <v>16</v>
       </c>
       <c r="I12" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -1584,16 +1618,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D13">
         <v>7</v>
       </c>
       <c r="E13" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F13" t="s">
         <v>16</v>
@@ -1605,7 +1639,7 @@
         <v>13</v>
       </c>
       <c r="L13" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -1613,10 +1647,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C14" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D14">
         <v>6</v>
@@ -1625,16 +1659,16 @@
         <v>15</v>
       </c>
       <c r="F14" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G14" t="s">
         <v>16</v>
       </c>
       <c r="I14" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="L14" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.3">
@@ -1642,39 +1676,39 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C15" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D15">
         <v>10</v>
       </c>
       <c r="E15" t="s">
+        <v>52</v>
+      </c>
+      <c r="F15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J15" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="F15" t="s">
-        <v>16</v>
-      </c>
-      <c r="G15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="K15" t="s">
-        <v>62</v>
+        <v>274</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C16" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D16">
         <v>6</v>
@@ -1683,27 +1717,27 @@
         <v>15</v>
       </c>
       <c r="F16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G16" t="s">
         <v>16</v>
       </c>
       <c r="I16" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>79</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B17" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C17" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D17">
         <v>6</v>
@@ -1712,30 +1746,30 @@
         <v>15</v>
       </c>
       <c r="F17" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G17" t="s">
         <v>16</v>
       </c>
       <c r="I17" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K17" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B18" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="C18" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="D18">
         <v>6</v>
@@ -1744,33 +1778,33 @@
         <v>15</v>
       </c>
       <c r="F18" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G18" t="s">
         <v>16</v>
       </c>
       <c r="I18" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J18" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="K18" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="L18" t="s">
-        <v>130</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B19" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="C19" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D19">
         <v>6</v>
@@ -1779,27 +1813,27 @@
         <v>15</v>
       </c>
       <c r="F19" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G19" t="s">
         <v>16</v>
       </c>
       <c r="I19" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="L19" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B20" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="C20" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D20">
         <v>6</v>
@@ -1808,62 +1842,62 @@
         <v>15</v>
       </c>
       <c r="F20" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G20" t="s">
         <v>16</v>
       </c>
       <c r="I20" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B21" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C21" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D21">
         <v>4</v>
       </c>
       <c r="E21" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="F21" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G21" t="s">
         <v>16</v>
       </c>
       <c r="L21" t="s">
-        <v>92</v>
+        <v>282</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B22" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="D22">
         <v>3</v>
       </c>
       <c r="E22" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="F22" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G22" t="s">
         <v>16</v>
@@ -1872,27 +1906,27 @@
         <v>12</v>
       </c>
       <c r="L22" t="s">
-        <v>96</v>
+        <v>284</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B23" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="C23" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="D23">
         <v>3</v>
       </c>
       <c r="E23" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="F23" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G23" t="s">
         <v>16</v>
@@ -1901,18 +1935,18 @@
         <v>12</v>
       </c>
       <c r="L23" t="s">
-        <v>99</v>
+        <v>285</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B24" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="C24" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -1921,50 +1955,50 @@
         <v>20</v>
       </c>
       <c r="F24" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G24" t="s">
         <v>16</v>
       </c>
       <c r="L24" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B25" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="C25" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="D25">
         <v>4</v>
       </c>
       <c r="E25" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="F25" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G25" t="s">
         <v>16</v>
       </c>
       <c r="L25" t="s">
-        <v>105</v>
+        <v>283</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B26" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="C26" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="D26">
         <v>6</v>
@@ -1979,21 +2013,21 @@
         <v>16</v>
       </c>
       <c r="I26" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B27" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="C27" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="D27">
         <v>6</v>
@@ -2002,27 +2036,27 @@
         <v>15</v>
       </c>
       <c r="F27" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G27" t="s">
         <v>16</v>
       </c>
       <c r="I27" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="L27" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B28" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="C28" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="D28">
         <v>6</v>
@@ -2037,10 +2071,10 @@
         <v>16</v>
       </c>
       <c r="I28" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>114</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>
@@ -2065,42 +2099,42 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -2112,13 +2146,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="21.5546875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B1" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -2126,7 +2163,7 @@
         <v>154</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>279</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -2134,7 +2171,7 @@
         <v>155</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -2149,10 +2186,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -2160,7 +2197,7 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -2178,10 +2215,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="B1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -2197,7 +2234,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -2205,7 +2242,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -2213,7 +2250,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -2221,7 +2258,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -2229,7 +2266,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -2268,10 +2305,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -2279,7 +2316,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -2287,7 +2324,7 @@
         <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -2295,7 +2332,7 @@
         <v>58</v>
       </c>
       <c r="B4" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -2303,7 +2340,7 @@
         <v>59</v>
       </c>
       <c r="B5" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -2311,7 +2348,7 @@
         <v>60</v>
       </c>
       <c r="B6" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -2319,7 +2356,7 @@
         <v>61</v>
       </c>
       <c r="B7" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -2327,7 +2364,7 @@
         <v>62</v>
       </c>
       <c r="B8" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -2335,7 +2372,7 @@
         <v>63</v>
       </c>
       <c r="B9" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -2343,7 +2380,7 @@
         <v>64</v>
       </c>
       <c r="B10" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -2351,7 +2388,7 @@
         <v>65</v>
       </c>
       <c r="B11" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -2359,7 +2396,7 @@
         <v>66</v>
       </c>
       <c r="B12" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -2367,7 +2404,7 @@
         <v>67</v>
       </c>
       <c r="B13" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
@@ -2375,7 +2412,7 @@
         <v>68</v>
       </c>
       <c r="B14" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
@@ -2383,7 +2420,7 @@
         <v>99</v>
       </c>
       <c r="B15" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
@@ -2391,7 +2428,7 @@
         <v>79</v>
       </c>
       <c r="B16" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
@@ -2399,7 +2436,7 @@
         <v>101</v>
       </c>
       <c r="B17" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
@@ -2407,7 +2444,7 @@
         <v>102</v>
       </c>
       <c r="B18" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
@@ -2415,7 +2452,7 @@
         <v>100</v>
       </c>
       <c r="B19" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
@@ -2423,7 +2460,7 @@
         <v>80</v>
       </c>
       <c r="B20" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
@@ -2431,7 +2468,7 @@
         <v>81</v>
       </c>
       <c r="B21" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
@@ -2439,7 +2476,7 @@
         <v>82</v>
       </c>
       <c r="B22" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
@@ -2447,7 +2484,7 @@
         <v>83</v>
       </c>
       <c r="B23" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
@@ -2455,7 +2492,7 @@
         <v>84</v>
       </c>
       <c r="B24" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -2470,498 +2507,498 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="B1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="B2" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="B3" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="B4" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="B5" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="B6" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="B7" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="B8" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="B9" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="B10" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="B11" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="B12" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="B13" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="B14" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="B15" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="B16" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="B17" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="B18" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="B19" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="B20" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="B21" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="B22" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="B23" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="B24" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="B25" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="B26" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="B27" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="B28" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="B29" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="B30" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="B31" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="B32" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="B33" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="B34" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="B35" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="B36" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="B37" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="B38" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="B39" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="B40" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="B41" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="B42" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="B43" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="B44" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="B45" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="B46" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="B47" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="B48" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
-        <v>272</v>
+        <v>259</v>
       </c>
       <c r="B49" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="B50" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="B51" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="B52" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="B53" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="B54" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="B55" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
-        <v>279</v>
+        <v>266</v>
       </c>
       <c r="B56" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
-        <v>280</v>
+        <v>267</v>
       </c>
       <c r="B57" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="B58" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
-        <v>282</v>
+        <v>269</v>
       </c>
       <c r="B59" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
-        <v>283</v>
+        <v>270</v>
       </c>
       <c r="B60" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
-        <v>284</v>
+        <v>271</v>
       </c>
       <c r="B61" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="B62" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>
@@ -2976,10 +3013,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -2987,7 +3024,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -2995,7 +3032,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -3003,7 +3040,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -3011,7 +3048,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -3019,7 +3056,7 @@
         <v>7</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -3027,7 +3064,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -3035,7 +3072,7 @@
         <v>9</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -3043,7 +3080,7 @@
         <v>10</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -3051,7 +3088,7 @@
         <v>11</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -3059,7 +3096,7 @@
         <v>12</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -3067,7 +3104,7 @@
         <v>13</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -3075,7 +3112,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
